--- a/Upgrade Go Live-SDCOE_PT86210_V2.xlsx
+++ b/Upgrade Go Live-SDCOE_PT86210_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\balaje\RAM\RAM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CFA660-739D-473A-AF75-A7C03E578955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601B1998-5ECA-4CA1-A416-58311B39BE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" tabRatio="744" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="744" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prod runs" sheetId="39" state="hidden" r:id="rId1"/>
@@ -41,9 +41,9 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Authorized User - Personal View" guid="{1EC65C91-6192-4F37-9147-E4740E0ED78F}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1148" windowHeight="735" tabRatio="655" activeSheetId="1" showFormulaBar="0" showStatusbar="0"/>
+    <customWorkbookView name="Employee - Personal View" guid="{B901C9D8-BD9F-41D2-A950-0E2BE3470D06}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="606" tabRatio="655" activeSheetId="3"/>
     <customWorkbookView name="Metro-North Railroad - Personal View" guid="{5E1CB5EF-277E-4B81-BAC8-452F91E8A5F7}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="606" tabRatio="655" activeSheetId="5"/>
-    <customWorkbookView name="Employee - Personal View" guid="{B901C9D8-BD9F-41D2-A950-0E2BE3470D06}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="606" tabRatio="655" activeSheetId="3"/>
-    <customWorkbookView name="Authorized User - Personal View" guid="{1EC65C91-6192-4F37-9147-E4740E0ED78F}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1148" windowHeight="735" tabRatio="655" activeSheetId="1" showFormulaBar="0" showStatusbar="0"/>
   </customWorkbookViews>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
@@ -735,9 +735,6 @@
     <t>Unlock remaining end-users locked for Upgrade</t>
   </si>
   <si>
-    <t>Create Production DB Restore points</t>
-  </si>
-  <si>
     <t>Bounce with clear cache on Web/App/Process scheduler servers</t>
   </si>
   <si>
@@ -748,9 +745,6 @@
   </si>
   <si>
     <t>COMM:  Notify SDCOE users of weekend down time.  Logistics for weekend validation</t>
-  </si>
-  <si>
-    <t>Provide List of IT User id's &amp; Business user id's to unlock for Validation(s)</t>
   </si>
   <si>
     <t>Peopletools Components &amp; Domain Creation on Production</t>
@@ -1060,6 +1054,12 @@
   </si>
   <si>
     <t>Sandeep/Chung</t>
+  </si>
+  <si>
+    <t>Create Production DB Restore points after validations</t>
+  </si>
+  <si>
+    <t>Provide List of IT User ID's &amp; Business User ID's to unlock for Validation(s)</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1578,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1769,17 +1769,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -1834,7 +1823,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2174,9 +2163,6 @@
     <xf numFmtId="0" fontId="44" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="44" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2202,7 +2188,7 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2355,7 +2341,7 @@
     <xf numFmtId="0" fontId="44" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2367,17 +2353,24 @@
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="5" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Hyperlink" xfId="5" builtinId="8"/>
@@ -3480,47 +3473,47 @@
     <col min="6" max="6" width="46.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="153" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+    <row r="1" spans="1:7" s="152" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="147" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="149" t="s">
+      <c r="B1" s="148" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="151" t="s">
+      <c r="D1" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="151" t="s">
+      <c r="E1" s="150" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="152" t="s">
+      <c r="F1" s="151" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="159" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="154" t="s">
-        <v>251</v>
-      </c>
-      <c r="B2" s="155"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="158"/>
+    <row r="2" spans="1:7" s="158" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="153" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="154"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="157"/>
     </row>
     <row r="3" spans="1:7" ht="14" x14ac:dyDescent="0.25">
       <c r="A3" s="79" t="s">
-        <v>227</v>
+        <v>272</v>
       </c>
       <c r="B3" s="90"/>
       <c r="C3" s="91"/>
       <c r="D3" s="93" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E3" s="92" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F3" s="95"/>
     </row>
@@ -3534,7 +3527,7 @@
         <v>50</v>
       </c>
       <c r="E4" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F4" s="94"/>
     </row>
@@ -3548,35 +3541,35 @@
         <v>50</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F5" s="94"/>
     </row>
     <row r="6" spans="1:7" ht="14" x14ac:dyDescent="0.25">
       <c r="A6" s="89" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B6" s="90"/>
       <c r="C6" s="91"/>
       <c r="D6" s="93" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E6" s="92" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F6" s="97"/>
     </row>
     <row r="7" spans="1:7" ht="14" x14ac:dyDescent="0.25">
       <c r="A7" s="89" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B7" s="90"/>
       <c r="C7" s="91"/>
       <c r="D7" s="93" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E7" s="92" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F7" s="95"/>
     </row>
@@ -3628,7 +3621,7 @@
     </row>
     <row r="11" spans="1:7" ht="28" x14ac:dyDescent="0.25">
       <c r="A11" s="89" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B11" s="98">
         <v>46288</v>
@@ -3638,14 +3631,14 @@
       <c r="E11" s="99"/>
       <c r="F11" s="94"/>
     </row>
-    <row r="12" spans="1:7" s="154" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="A12" s="154" t="s">
-        <v>228</v>
+    <row r="12" spans="1:7" s="153" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="A12" s="153" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28" x14ac:dyDescent="0.25">
       <c r="A13" s="79" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B13" s="90">
         <v>46283</v>
@@ -3655,13 +3648,13 @@
         <v>50</v>
       </c>
       <c r="E13" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F13" s="95"/>
     </row>
     <row r="14" spans="1:7" ht="28" x14ac:dyDescent="0.25">
       <c r="A14" s="79" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B14" s="90">
         <v>46283</v>
@@ -3671,13 +3664,13 @@
         <v>50</v>
       </c>
       <c r="E14" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F14" s="101"/>
     </row>
     <row r="15" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="79" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B15" s="90">
         <v>46283</v>
@@ -3687,14 +3680,14 @@
         <v>50</v>
       </c>
       <c r="E15" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F15" s="94"/>
       <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="79" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B16" s="90">
         <v>46283</v>
@@ -3704,14 +3697,14 @@
         <v>50</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F16" s="94"/>
       <c r="G16" s="54"/>
     </row>
     <row r="17" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="79" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B17" s="90">
         <v>46283</v>
@@ -3721,14 +3714,14 @@
         <v>50</v>
       </c>
       <c r="E17" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F17" s="97"/>
       <c r="G17" s="54"/>
     </row>
     <row r="18" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="102" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B18" s="90">
         <v>46283</v>
@@ -3738,14 +3731,14 @@
         <v>50</v>
       </c>
       <c r="E18" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F18" s="97"/>
       <c r="G18" s="54"/>
     </row>
     <row r="19" spans="1:7" ht="14" x14ac:dyDescent="0.3">
       <c r="A19" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B19" s="104">
         <v>46283</v>
@@ -3755,7 +3748,7 @@
         <v>50</v>
       </c>
       <c r="E19" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F19" s="105"/>
     </row>
@@ -3764,7 +3757,7 @@
     <sortCondition ref="B4:B13"/>
     <sortCondition ref="D4:D13"/>
   </sortState>
-  <conditionalFormatting sqref="C13:C19 C2:C11">
+  <conditionalFormatting sqref="C2:C11 C13:C19">
     <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="Pending">
       <formula>NOT(ISERROR(SEARCH("Pending",C2)))</formula>
     </cfRule>
@@ -3805,53 +3798,53 @@
     <col min="8" max="16384" width="16.453125" style="80"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="148" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="B1" s="148" t="s">
+    <row r="1" spans="1:7" s="147" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="B1" s="147" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="147" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="148" t="s">
+      <c r="D1" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="148" t="s">
+      <c r="E1" s="147" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="148" t="s">
+      <c r="F1" s="147" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="148" t="s">
+      <c r="G1" s="147" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="165" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="160"/>
-      <c r="B2" s="161" t="s">
+    <row r="2" spans="1:7" s="164" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="159"/>
+      <c r="B2" s="160" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="162"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="164"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="163"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="106" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="78" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C3" s="107">
         <v>0</v>
       </c>
       <c r="D3" s="91"/>
       <c r="E3" s="108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F3" s="108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G3" s="94"/>
     </row>
@@ -3908,7 +3901,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G6" s="94"/>
     </row>
@@ -3927,7 +3920,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G7" s="110"/>
     </row>
@@ -3936,17 +3929,17 @@
         <v>5</v>
       </c>
       <c r="B8" s="79" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C8" s="107">
         <v>0</v>
       </c>
       <c r="D8" s="91"/>
       <c r="E8" s="108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F8" s="108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G8" s="111"/>
     </row>
@@ -3962,40 +3955,40 @@
       </c>
       <c r="D9" s="91"/>
       <c r="E9" s="96" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F9" s="108" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G9" s="95"/>
     </row>
-    <row r="10" spans="1:7" s="171" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="166"/>
-      <c r="B10" s="167" t="s">
+    <row r="10" spans="1:7" s="170" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="165"/>
+      <c r="B10" s="166" t="s">
         <v>196</v>
       </c>
-      <c r="C10" s="168"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="170"/>
+      <c r="C10" s="167"/>
+      <c r="D10" s="168"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="169"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="106">
         <v>7</v>
       </c>
       <c r="B11" s="79" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C11" s="107">
         <v>0</v>
       </c>
       <c r="D11" s="91"/>
       <c r="E11" s="108" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F11" s="108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G11" s="112"/>
     </row>
@@ -4011,10 +4004,10 @@
       </c>
       <c r="D12" s="91"/>
       <c r="E12" s="108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F12" s="108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G12" s="110"/>
     </row>
@@ -4033,7 +4026,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G13" s="79"/>
     </row>
@@ -4041,7 +4034,7 @@
       <c r="A14" s="96">
         <v>10</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="209" t="s">
         <v>198</v>
       </c>
       <c r="C14" s="113">
@@ -4071,7 +4064,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G15" s="79"/>
     </row>
@@ -4090,7 +4083,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G16" s="114"/>
     </row>
@@ -4109,7 +4102,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G17" s="115"/>
     </row>
@@ -4128,7 +4121,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G18" s="116"/>
     </row>
@@ -4147,7 +4140,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G19" s="116"/>
     </row>
@@ -4166,7 +4159,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G20" s="116"/>
     </row>
@@ -4185,7 +4178,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G21" s="116"/>
     </row>
@@ -4204,7 +4197,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G22" s="116"/>
     </row>
@@ -4223,7 +4216,7 @@
         <v>50</v>
       </c>
       <c r="F23" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G23" s="116"/>
     </row>
@@ -4242,7 +4235,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G24" s="117"/>
     </row>
@@ -4261,7 +4254,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G25" s="116"/>
     </row>
@@ -4280,7 +4273,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G26" s="119"/>
     </row>
@@ -4299,7 +4292,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G27" s="119"/>
     </row>
@@ -4318,7 +4311,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G28" s="119"/>
     </row>
@@ -4326,8 +4319,8 @@
       <c r="A29" s="96">
         <v>25</v>
       </c>
-      <c r="B29" s="79" t="s">
-        <v>237</v>
+      <c r="B29" s="209" t="s">
+        <v>235</v>
       </c>
       <c r="C29" s="118">
         <v>1.3888888888888888E-2</v>
@@ -4346,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="120" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C30" s="113">
         <v>0</v>
@@ -4356,20 +4349,20 @@
         <v>50</v>
       </c>
       <c r="F30" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G30" s="79"/>
     </row>
-    <row r="31" spans="1:7" s="171" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="166"/>
-      <c r="B31" s="167" t="s">
+    <row r="31" spans="1:7" s="170" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="165"/>
+      <c r="B31" s="166" t="s">
         <v>77</v>
       </c>
-      <c r="C31" s="168"/>
-      <c r="D31" s="169"/>
-      <c r="E31" s="167"/>
-      <c r="F31" s="172"/>
-      <c r="G31" s="173"/>
+      <c r="C31" s="167"/>
+      <c r="D31" s="168"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="171"/>
+      <c r="G31" s="172"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="96">
@@ -4407,7 +4400,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G33" s="126"/>
     </row>
@@ -4426,7 +4419,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G34" s="126"/>
     </row>
@@ -4445,7 +4438,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G35" s="126"/>
     </row>
@@ -4454,7 +4447,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="121" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C36" s="113">
         <v>2.7777777777777776E-2</v>
@@ -4464,7 +4457,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G36" s="126"/>
     </row>
@@ -4483,7 +4476,7 @@
         <v>50</v>
       </c>
       <c r="F37" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G37" s="127"/>
     </row>
@@ -4502,7 +4495,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G38" s="127"/>
     </row>
@@ -4521,7 +4514,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G39" s="126"/>
       <c r="H39" s="80"/>
@@ -4541,17 +4534,17 @@
         <v>50</v>
       </c>
       <c r="F40" s="93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G40" s="126"/>
       <c r="H40" s="80"/>
     </row>
     <row r="41" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="141">
+      <c r="A41" s="140">
         <v>36</v>
       </c>
       <c r="B41" s="121" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C41" s="131">
         <v>6.9444444444444441E-3</v>
@@ -4567,7 +4560,7 @@
       <c r="H41" s="80"/>
     </row>
     <row r="42" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="147">
+      <c r="A42" s="146">
         <v>37</v>
       </c>
       <c r="B42" s="121" t="s">
@@ -4581,7 +4574,7 @@
         <v>50</v>
       </c>
       <c r="F42" s="124" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G42" s="126"/>
       <c r="H42" s="80"/>
@@ -4621,7 +4614,7 @@
         <v>50</v>
       </c>
       <c r="F44" s="124" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G44" s="126"/>
       <c r="H44" s="80"/>
@@ -4641,9 +4634,9 @@
         <v>50</v>
       </c>
       <c r="F45" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="G45" s="201"/>
+        <v>238</v>
+      </c>
+      <c r="G45" s="200"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="135">
@@ -4660,9 +4653,9 @@
         <v>50</v>
       </c>
       <c r="F46" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="G46" s="201"/>
+        <v>238</v>
+      </c>
+      <c r="G46" s="200"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="135">
@@ -4679,9 +4672,9 @@
         <v>50</v>
       </c>
       <c r="F47" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="G47" s="201"/>
+        <v>238</v>
+      </c>
+      <c r="G47" s="200"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="135">
@@ -4693,41 +4686,41 @@
       <c r="C48" s="133">
         <v>0</v>
       </c>
-      <c r="D48" s="91"/>
+      <c r="D48" s="134"/>
       <c r="E48" s="96" t="s">
         <v>50</v>
       </c>
       <c r="F48" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="G48" s="201"/>
+        <v>238</v>
+      </c>
+      <c r="G48" s="200"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="137">
         <v>44</v>
       </c>
-      <c r="B49" s="207" t="s">
-        <v>258</v>
-      </c>
-      <c r="C49" s="138">
+      <c r="B49" s="211" t="s">
+        <v>256</v>
+      </c>
+      <c r="C49" s="131">
         <v>0.125</v>
       </c>
-      <c r="D49" s="91"/>
+      <c r="D49" s="134"/>
       <c r="E49" s="96" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F49" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="G49" s="202"/>
+        <v>238</v>
+      </c>
+      <c r="G49" s="201"/>
       <c r="H49" s="84"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" s="137">
         <v>45</v>
       </c>
-      <c r="B50" s="136" t="s">
-        <v>222</v>
+      <c r="B50" s="210" t="s">
+        <v>271</v>
       </c>
       <c r="C50" s="131">
         <v>1.3888888888888888E-2</v>
@@ -4739,7 +4732,7 @@
       <c r="F50" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="G50" s="202"/>
+      <c r="G50" s="201"/>
       <c r="H50" s="84"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.4">
@@ -4747,7 +4740,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="120" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C51" s="122">
         <v>0</v>
@@ -4757,16 +4750,16 @@
         <v>50</v>
       </c>
       <c r="F51" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="G51" s="143"/>
-      <c r="H51" s="206"/>
+        <v>238</v>
+      </c>
+      <c r="G51" s="142"/>
+      <c r="H51" s="205"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" s="108">
         <v>47</v>
       </c>
-      <c r="B52" s="209" t="s">
+      <c r="B52" s="207" t="s">
         <v>216</v>
       </c>
       <c r="C52" s="122">
@@ -4774,10 +4767,10 @@
       </c>
       <c r="D52" s="91"/>
       <c r="E52" s="96" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F52" s="124" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G52" s="126"/>
       <c r="H52" s="84"/>
@@ -4786,8 +4779,8 @@
       <c r="A53" s="108">
         <v>48</v>
       </c>
-      <c r="B53" s="210" t="s">
-        <v>269</v>
+      <c r="B53" s="208" t="s">
+        <v>267</v>
       </c>
       <c r="C53" s="129">
         <v>0.27083333333333331</v>
@@ -4799,7 +4792,7 @@
       <c r="H53" s="84"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A54" s="208">
+      <c r="A54" s="206">
         <v>49</v>
       </c>
       <c r="B54" s="136" t="s">
@@ -4813,13 +4806,13 @@
         <v>50</v>
       </c>
       <c r="F54" s="124" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G54" s="126"/>
       <c r="H54" s="84"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A55" s="139">
+      <c r="A55" s="138">
         <v>50</v>
       </c>
       <c r="B55" s="136" t="s">
@@ -4829,20 +4822,20 @@
         <v>6.9444444444444441E-3</v>
       </c>
       <c r="D55" s="91"/>
-      <c r="E55" s="142" t="s">
-        <v>50</v>
-      </c>
-      <c r="F55" s="142" t="s">
-        <v>238</v>
+      <c r="E55" s="141" t="s">
+        <v>50</v>
+      </c>
+      <c r="F55" s="141" t="s">
+        <v>236</v>
       </c>
       <c r="G55" s="126"/>
       <c r="H55" s="84"/>
     </row>
     <row r="56" spans="1:11" s="81" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="141">
+      <c r="A56" s="140">
         <v>51</v>
       </c>
-      <c r="B56" s="174" t="s">
+      <c r="B56" s="173" t="s">
         <v>220</v>
       </c>
       <c r="C56" s="113">
@@ -4850,18 +4843,18 @@
       </c>
       <c r="D56" s="91"/>
       <c r="E56" s="124" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F56" s="124" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G56" s="126"/>
     </row>
     <row r="57" spans="1:11" s="81" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="139">
+      <c r="A57" s="138">
         <v>52</v>
       </c>
-      <c r="B57" s="174" t="s">
+      <c r="B57" s="173" t="s">
         <v>82</v>
       </c>
       <c r="C57" s="113">
@@ -4869,32 +4862,32 @@
       </c>
       <c r="D57" s="91"/>
       <c r="E57" s="124" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F57" s="124" t="s">
-        <v>238</v>
-      </c>
-      <c r="G57" s="143"/>
-    </row>
-    <row r="58" spans="1:11" s="161" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="A58" s="161" t="s">
+        <v>236</v>
+      </c>
+      <c r="G57" s="142"/>
+    </row>
+    <row r="58" spans="1:11" s="160" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="A58" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="B58" s="161" t="s">
+      <c r="B58" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="G58" s="203"/>
-      <c r="H58" s="205"/>
-      <c r="I58" s="205"/>
-      <c r="J58" s="205"/>
-      <c r="K58" s="204"/>
+      <c r="G58" s="202"/>
+      <c r="H58" s="204"/>
+      <c r="I58" s="204"/>
+      <c r="J58" s="204"/>
+      <c r="K58" s="203"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A59" s="85">
         <v>53</v>
       </c>
       <c r="B59" s="136" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C59" s="122">
         <v>0</v>
@@ -4904,16 +4897,16 @@
         <v>50</v>
       </c>
       <c r="F59" s="93" t="s">
-        <v>240</v>
-      </c>
-      <c r="G59" s="144"/>
+        <v>238</v>
+      </c>
+      <c r="G59" s="143"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A60" s="108">
         <v>54</v>
       </c>
       <c r="B60" s="79" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C60" s="122"/>
       <c r="D60" s="91"/>
@@ -4923,7 +4916,7 @@
       <c r="F60" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="G60" s="144"/>
+      <c r="G60" s="143"/>
     </row>
     <row r="61" spans="1:11" s="81" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A61" s="96">
@@ -4940,28 +4933,28 @@
         <v>50</v>
       </c>
       <c r="F61" s="93" t="s">
-        <v>240</v>
-      </c>
-      <c r="G61" s="145"/>
+        <v>238</v>
+      </c>
+      <c r="G61" s="144"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A62" s="96">
         <v>56</v>
       </c>
       <c r="B62" s="79" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C62" s="122">
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="D62" s="91"/>
       <c r="E62" s="96" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F62" s="124" t="s">
-        <v>246</v>
-      </c>
-      <c r="G62" s="140"/>
+        <v>244</v>
+      </c>
+      <c r="G62" s="139"/>
       <c r="H62" s="84"/>
     </row>
     <row r="63" spans="1:11" s="81" customFormat="1" x14ac:dyDescent="0.4">
@@ -4969,26 +4962,26 @@
         <v>57</v>
       </c>
       <c r="B63" s="79" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C63" s="113">
         <v>6.9444444444444441E-3</v>
       </c>
       <c r="D63" s="91"/>
       <c r="E63" s="108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F63" s="124" t="s">
-        <v>238</v>
-      </c>
-      <c r="G63" s="146"/>
+        <v>236</v>
+      </c>
+      <c r="G63" s="145"/>
     </row>
     <row r="64" spans="1:11" s="81" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A64" s="96">
         <v>58</v>
       </c>
       <c r="B64" s="79" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C64" s="113">
         <v>4.1666666666666664E-2</v>
@@ -5065,20 +5058,20 @@
     <col min="8" max="16384" width="23.54296875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="178" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="175" t="s">
-        <v>259</v>
-      </c>
-      <c r="B1" s="176" t="s">
+    <row r="1" spans="1:5" s="177" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="174" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="175" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="177" t="s">
+      <c r="C1" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="176" t="s">
+      <c r="D1" s="175" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="176" t="s">
+      <c r="E1" s="175" t="s">
         <v>84</v>
       </c>
     </row>
@@ -5108,7 +5101,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="64" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B4" s="27"/>
       <c r="C4" s="67"/>
@@ -5130,7 +5123,7 @@
     </row>
     <row r="6" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="64" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="67"/>
@@ -5141,7 +5134,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="64" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="67"/>
@@ -5163,7 +5156,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="69"/>
@@ -5196,7 +5189,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="64" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="67"/>
@@ -5207,7 +5200,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="64" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B13" s="27"/>
       <c r="C13" s="67"/>
@@ -5218,7 +5211,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="64" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B14" s="27"/>
       <c r="C14" s="67"/>
@@ -5251,7 +5244,7 @@
     </row>
     <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="77" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="27"/>
@@ -5305,92 +5298,92 @@
       <c r="E21" s="27"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="191" t="s">
+      <c r="A22" s="190" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="192"/>
-      <c r="C22" s="192"/>
-      <c r="D22" s="193" t="s">
+      <c r="B22" s="191"/>
+      <c r="C22" s="191"/>
+      <c r="D22" s="192" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="27"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="194" t="s">
-        <v>264</v>
-      </c>
-      <c r="B23" s="195"/>
-      <c r="C23" s="198"/>
-      <c r="D23" s="199" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="200"/>
+      <c r="A23" s="193" t="s">
+        <v>262</v>
+      </c>
+      <c r="B23" s="194"/>
+      <c r="C23" s="197"/>
+      <c r="D23" s="198" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="199"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="194" t="s">
+      <c r="A24" s="193" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="195"/>
-      <c r="C24" s="196"/>
-      <c r="D24" s="197" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="195"/>
+      <c r="B24" s="194"/>
+      <c r="C24" s="195"/>
+      <c r="D24" s="196" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="194"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="194" t="s">
+      <c r="A25" s="193" t="s">
         <v>212</v>
       </c>
-      <c r="B25" s="195"/>
-      <c r="C25" s="195"/>
-      <c r="D25" s="197" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="195"/>
+      <c r="B25" s="194"/>
+      <c r="C25" s="194"/>
+      <c r="D25" s="196" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="194"/>
     </row>
     <row r="26" spans="1:5" ht="28" x14ac:dyDescent="0.3">
-      <c r="A26" s="194" t="s">
+      <c r="A26" s="193" t="s">
         <v>213</v>
       </c>
-      <c r="B26" s="195"/>
-      <c r="C26" s="195"/>
-      <c r="D26" s="197" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="195"/>
+      <c r="B26" s="194"/>
+      <c r="C26" s="194"/>
+      <c r="D26" s="196" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="194"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="194" t="s">
+      <c r="A27" s="193" t="s">
         <v>214</v>
       </c>
-      <c r="B27" s="195"/>
-      <c r="C27" s="195"/>
-      <c r="D27" s="197" t="s">
-        <v>50</v>
-      </c>
-      <c r="E27" s="195"/>
+      <c r="B27" s="194"/>
+      <c r="C27" s="194"/>
+      <c r="D27" s="196" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="194"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="194" t="s">
+      <c r="A28" s="193" t="s">
         <v>215</v>
       </c>
-      <c r="B28" s="195"/>
-      <c r="C28" s="195"/>
-      <c r="D28" s="197" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="195"/>
+      <c r="B28" s="194"/>
+      <c r="C28" s="194"/>
+      <c r="D28" s="196" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="194"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="194" t="s">
+      <c r="A29" s="193" t="s">
         <v>218</v>
       </c>
-      <c r="B29" s="195"/>
-      <c r="C29" s="195"/>
-      <c r="D29" s="197" t="s">
-        <v>50</v>
-      </c>
-      <c r="E29" s="195"/>
+      <c r="B29" s="194"/>
+      <c r="C29" s="194"/>
+      <c r="D29" s="196" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="194"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
@@ -5437,46 +5430,46 @@
     <col min="25" max="16384" width="14.453125" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="184" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="179" t="s">
+    <row r="1" spans="1:7" s="183" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="178" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="180" t="s">
+      <c r="B1" s="179" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="181" t="s">
+      <c r="C1" s="180" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="179" t="s">
+      <c r="D1" s="178" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="182" t="s">
+      <c r="E1" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="182" t="s">
+      <c r="F1" s="181" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="183" t="s">
+      <c r="G1" s="182" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="190" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="185"/>
-      <c r="B2" s="186" t="s">
+    <row r="2" spans="1:7" s="189" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="184"/>
+      <c r="B2" s="185" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="189" t="s">
+      <c r="C2" s="186"/>
+      <c r="D2" s="187"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="188" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="72" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="55"/>
       <c r="B3" s="70" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C3" s="60">
         <v>0</v>
@@ -5485,10 +5478,10 @@
         <v>29</v>
       </c>
       <c r="E3" s="66" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F3" s="66" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G3" s="61"/>
     </row>
@@ -5497,7 +5490,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C4" s="56">
         <v>1.0416666666666666E-2</v>
@@ -5506,10 +5499,10 @@
         <v>29</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G4" s="76"/>
     </row>
@@ -5530,7 +5523,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G5" s="61"/>
     </row>
@@ -5551,7 +5544,7 @@
         <v>59</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G6" s="62"/>
     </row>
@@ -5572,7 +5565,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G7" s="62"/>
     </row>
@@ -5581,7 +5574,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C8" s="56">
         <v>1.0416666666666666E-2</v>
@@ -5593,7 +5586,7 @@
         <v>50</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G8" s="61"/>
     </row>
@@ -5611,17 +5604,17 @@
         <v>29</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G9" s="61"/>
     </row>
     <row r="10" spans="1:7" s="72" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="55"/>
       <c r="B10" s="70" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C10" s="60">
         <v>0</v>
@@ -5630,10 +5623,10 @@
         <v>29</v>
       </c>
       <c r="E10" s="66" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F10" s="66" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G10" s="61"/>
     </row>
@@ -6424,17 +6417,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dddba757-1223-457f-9a11-7ee2fbfa584c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8b191620-0153-4acc-a89a-219ae713f494" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AB818DA128A67242B083C5FBA2577CEE" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="45aa763b12272e983fcc30a9438fec5b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dddba757-1223-457f-9a11-7ee2fbfa584c" xmlns:ns3="3d99c943-a120-4774-ac99-24b2effbc1ca" xmlns:ns4="8b191620-0153-4acc-a89a-219ae713f494" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="420e5935653a350c8e079bd3f68b2c52" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="dddba757-1223-457f-9a11-7ee2fbfa584c"/>
@@ -6674,6 +6656,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dddba757-1223-457f-9a11-7ee2fbfa584c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8b191620-0153-4acc-a89a-219ae713f494" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA22AA7A-CA8E-4821-A082-8450591566E1}">
   <ds:schemaRefs>
@@ -6683,17 +6676,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9DC29D4-D600-4977-AD7C-ED927A18CC0C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dddba757-1223-457f-9a11-7ee2fbfa584c"/>
-    <ds:schemaRef ds:uri="8b191620-0153-4acc-a89a-219ae713f494"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9471089-06E4-4832-9E01-A3A0E3A8194E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6713,6 +6695,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9DC29D4-D600-4977-AD7C-ED927A18CC0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dddba757-1223-457f-9a11-7ee2fbfa584c"/>
+    <ds:schemaRef ds:uri="8b191620-0153-4acc-a89a-219ae713f494"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{2199bfba-a409-4f13-b0c4-18b45933d88d}" enabled="0" method="" siteId="{2199bfba-a409-4f13-b0c4-18b45933d88d}" removed="1"/>
